--- a/bin/Debug/H5509_alarm.xlsx
+++ b/bin/Debug/H5509_alarm.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12960"/>
+    <workbookView windowWidth="26385" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3690" uniqueCount="2451">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3693" uniqueCount="2452">
   <si>
     <t>C_EmptySidePush--Cylinder On Sensor Can not Detect On</t>
   </si>
@@ -7383,6 +7383,9 @@
   </si>
   <si>
     <t>全部回零完成</t>
+  </si>
+  <si>
+    <t>设备未归零</t>
   </si>
 </sst>
 </file>
@@ -8325,7 +8328,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1230"/>
+  <dimension ref="A1:E1231"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="3.5" style="1" customWidth="1"/>
@@ -29248,6 +29251,23 @@
         <v>2336</v>
       </c>
     </row>
+    <row r="1231" spans="1:5">
+      <c r="A1231" s="1">
+        <v>17</v>
+      </c>
+      <c r="B1231" s="1">
+        <v>1400445</v>
+      </c>
+      <c r="C1231" s="2" t="s">
+        <v>2451</v>
+      </c>
+      <c r="D1231" s="2" t="s">
+        <v>2451</v>
+      </c>
+      <c r="E1231" s="1" t="s">
+        <v>2347</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:E1230" etc:filterBottomFollowUsedRange="0">
     <extLst/>

--- a/bin/Debug/H5509_alarm.xlsx
+++ b/bin/Debug/H5509_alarm.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="26385" windowHeight="13020"/>
+    <workbookView windowWidth="27945" windowHeight="12960"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4077" uniqueCount="2608">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4086" uniqueCount="2611">
   <si>
     <t>C_EmptySidePush--Cylinder On Sensor Can not Detect On</t>
   </si>
@@ -7854,6 +7854,15 @@
   </si>
   <si>
     <t>设备未归零</t>
+  </si>
+  <si>
+    <t>升温超时</t>
+  </si>
+  <si>
+    <t>设定温度失败</t>
+  </si>
+  <si>
+    <t>温控器连接失败</t>
   </si>
 </sst>
 </file>
@@ -8538,13 +8547,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
-<customStorage xmlns="https://web.wps.cn/et/2018/main">
-  <book/>
-  <sheets/>
-</customStorage>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -8803,7 +8805,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1359"/>
+  <dimension ref="A1:E1362"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="3.5" style="1" customWidth="1"/>
@@ -31919,6 +31921,57 @@
         <v>1093</v>
       </c>
     </row>
+    <row r="1360" spans="1:5">
+      <c r="A1360" s="1">
+        <v>17</v>
+      </c>
+      <c r="B1360" s="1">
+        <v>1400446</v>
+      </c>
+      <c r="C1360" s="2" t="s">
+        <v>2608</v>
+      </c>
+      <c r="D1360" s="2" t="s">
+        <v>2608</v>
+      </c>
+      <c r="E1360" s="1" t="s">
+        <v>2428</v>
+      </c>
+    </row>
+    <row r="1361" spans="1:5">
+      <c r="A1361" s="1">
+        <v>17</v>
+      </c>
+      <c r="B1361" s="1">
+        <v>1400447</v>
+      </c>
+      <c r="C1361" s="2" t="s">
+        <v>2609</v>
+      </c>
+      <c r="D1361" s="2" t="s">
+        <v>2609</v>
+      </c>
+      <c r="E1361" s="1" t="s">
+        <v>2428</v>
+      </c>
+    </row>
+    <row r="1362" spans="1:5">
+      <c r="A1362" s="1">
+        <v>17</v>
+      </c>
+      <c r="B1362" s="1">
+        <v>1400448</v>
+      </c>
+      <c r="C1362" s="2" t="s">
+        <v>2610</v>
+      </c>
+      <c r="D1362" s="2" t="s">
+        <v>2610</v>
+      </c>
+      <c r="E1362" s="1" t="s">
+        <v>2428</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:E1359" etc:filterBottomFollowUsedRange="0">
     <extLst/>

--- a/bin/Debug/H5509_alarm.xlsx
+++ b/bin/Debug/H5509_alarm.xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12960"/>
+    <workbookView windowWidth="28800" windowHeight="12960"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$1359</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$1362</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4086" uniqueCount="2611">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4113" uniqueCount="2630">
   <si>
     <t>C_EmptySidePush--Cylinder On Sensor Can not Detect On</t>
   </si>
@@ -7817,7 +7817,7 @@
     <t>ALL Home Exception</t>
   </si>
   <si>
-    <t>全部回零异常</t>
+    <t>全部回零异常!详细信息:Msg</t>
   </si>
   <si>
     <t>Com Not Open</t>
@@ -7863,6 +7863,63 @@
   </si>
   <si>
     <t>温控器连接失败</t>
+  </si>
+  <si>
+    <t>温控器连接失败!</t>
+  </si>
+  <si>
+    <t>读取Site1-Site8探测温度失败</t>
+  </si>
+  <si>
+    <t>读取Site1-Site8温度失败!详细信息:Msg</t>
+  </si>
+  <si>
+    <t>读取Site9-Site16探测温度失败</t>
+  </si>
+  <si>
+    <t>读取Site9-Site16温度失败!详细信息:Msg</t>
+  </si>
+  <si>
+    <t>读取加热盘探测温度失败</t>
+  </si>
+  <si>
+    <t>读取加热盘温度失败!详细信息:Msg</t>
+  </si>
+  <si>
+    <t>设定Site1-Site8温度失败</t>
+  </si>
+  <si>
+    <t>设定Site1-Site8温度失败!详细信息:Msg</t>
+  </si>
+  <si>
+    <t>设定Site9-Site16温度失败</t>
+  </si>
+  <si>
+    <t>设定Site9-Site16温度失败!详细信息:Msg</t>
+  </si>
+  <si>
+    <t>设定加热盘温度失败</t>
+  </si>
+  <si>
+    <t>设定加热盘温度失败!详细信息:Msg</t>
+  </si>
+  <si>
+    <t>读取Site1-Site8设定温度失败</t>
+  </si>
+  <si>
+    <t>读取Site1-Site8设定温度失败!详细信息:Msg</t>
+  </si>
+  <si>
+    <t>读取Site9-Site16设定温度失败</t>
+  </si>
+  <si>
+    <t>读取Site9-Site16设定温度失败!详细信息:Msg</t>
+  </si>
+  <si>
+    <t>读取加热盘设定温度失败</t>
+  </si>
+  <si>
+    <t>读取加热盘设定温度失败!详细信息:Msg</t>
   </si>
 </sst>
 </file>
@@ -8805,7 +8862,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1362"/>
+  <dimension ref="A1:E1371"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="3.5" style="1" customWidth="1"/>
@@ -31966,14 +32023,167 @@
         <v>2610</v>
       </c>
       <c r="D1362" s="2" t="s">
-        <v>2610</v>
+        <v>2611</v>
       </c>
       <c r="E1362" s="1" t="s">
         <v>2428</v>
       </c>
     </row>
+    <row r="1363" spans="1:5">
+      <c r="A1363" s="1">
+        <v>17</v>
+      </c>
+      <c r="B1363" s="1">
+        <v>1400449</v>
+      </c>
+      <c r="C1363" s="2" t="s">
+        <v>2612</v>
+      </c>
+      <c r="D1363" s="2" t="s">
+        <v>2613</v>
+      </c>
+      <c r="E1363" s="1" t="s">
+        <v>2428</v>
+      </c>
+    </row>
+    <row r="1364" spans="1:5">
+      <c r="A1364" s="1">
+        <v>17</v>
+      </c>
+      <c r="B1364" s="1">
+        <v>1400450</v>
+      </c>
+      <c r="C1364" s="2" t="s">
+        <v>2614</v>
+      </c>
+      <c r="D1364" s="2" t="s">
+        <v>2615</v>
+      </c>
+      <c r="E1364" s="1" t="s">
+        <v>2428</v>
+      </c>
+    </row>
+    <row r="1365" spans="1:5">
+      <c r="A1365" s="1">
+        <v>17</v>
+      </c>
+      <c r="B1365" s="1">
+        <v>1400451</v>
+      </c>
+      <c r="C1365" s="2" t="s">
+        <v>2616</v>
+      </c>
+      <c r="D1365" s="2" t="s">
+        <v>2617</v>
+      </c>
+      <c r="E1365" s="1" t="s">
+        <v>2428</v>
+      </c>
+    </row>
+    <row r="1366" spans="1:5">
+      <c r="A1366" s="1">
+        <v>17</v>
+      </c>
+      <c r="B1366" s="1">
+        <v>1400452</v>
+      </c>
+      <c r="C1366" s="2" t="s">
+        <v>2618</v>
+      </c>
+      <c r="D1366" s="2" t="s">
+        <v>2619</v>
+      </c>
+      <c r="E1366" s="1" t="s">
+        <v>2428</v>
+      </c>
+    </row>
+    <row r="1367" spans="1:5">
+      <c r="A1367" s="1">
+        <v>17</v>
+      </c>
+      <c r="B1367" s="1">
+        <v>1400453</v>
+      </c>
+      <c r="C1367" s="2" t="s">
+        <v>2620</v>
+      </c>
+      <c r="D1367" s="2" t="s">
+        <v>2621</v>
+      </c>
+      <c r="E1367" s="1" t="s">
+        <v>2428</v>
+      </c>
+    </row>
+    <row r="1368" spans="1:5">
+      <c r="A1368" s="1">
+        <v>17</v>
+      </c>
+      <c r="B1368" s="1">
+        <v>1400454</v>
+      </c>
+      <c r="C1368" s="2" t="s">
+        <v>2622</v>
+      </c>
+      <c r="D1368" s="2" t="s">
+        <v>2623</v>
+      </c>
+      <c r="E1368" s="1" t="s">
+        <v>2428</v>
+      </c>
+    </row>
+    <row r="1369" spans="1:5">
+      <c r="A1369" s="1">
+        <v>17</v>
+      </c>
+      <c r="B1369" s="1">
+        <v>1400455</v>
+      </c>
+      <c r="C1369" s="2" t="s">
+        <v>2624</v>
+      </c>
+      <c r="D1369" s="2" t="s">
+        <v>2625</v>
+      </c>
+      <c r="E1369" s="1" t="s">
+        <v>2428</v>
+      </c>
+    </row>
+    <row r="1370" spans="1:5">
+      <c r="A1370" s="1">
+        <v>17</v>
+      </c>
+      <c r="B1370" s="1">
+        <v>1400456</v>
+      </c>
+      <c r="C1370" s="2" t="s">
+        <v>2626</v>
+      </c>
+      <c r="D1370" s="2" t="s">
+        <v>2627</v>
+      </c>
+      <c r="E1370" s="1" t="s">
+        <v>2428</v>
+      </c>
+    </row>
+    <row r="1371" spans="1:5">
+      <c r="A1371" s="1">
+        <v>17</v>
+      </c>
+      <c r="B1371" s="1">
+        <v>1400457</v>
+      </c>
+      <c r="C1371" s="2" t="s">
+        <v>2628</v>
+      </c>
+      <c r="D1371" s="2" t="s">
+        <v>2629</v>
+      </c>
+      <c r="E1371" s="1" t="s">
+        <v>2428</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:E1359" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:E1362" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
